--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_09_Full_107_Cau/Day_09_Ngan_Hang_Phan_04_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_09_Full_107_Cau/Day_09_Ngan_Hang_Phan_04_21_Cau.xlsx
@@ -727,7 +727,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Thiết kế cả đường không nhận việc và không hoàn tất.</t>
+          <t>Yêu cầu ủy thác công việc giữa các agent thuộc các bên sở hữu khác nhau (Agent-to-Agent delegation) cần: (a) Định nghĩa nhiệm vụ và ngữ cảnh được giới hạn chặt chẽ; (b) Các ràng buộc và định dạng artifact đầu ra mong đợi; (c) Thời hạn hoàn thành (deadline), trạng thái hoặc cơ chế callback; (d) Ngữ nghĩa rõ ràng cho các trạng thái: nhận việc, từ chối, timeout, và hoàn thành một phần. Tuyệt đối không chia sẻ toàn bộ state nội bộ và bí mật.</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bản sửa phải quay lại verifier; không thử lại trước khi có feedback có thể hành động.</t>
+          <t>Trình tự vòng lặp phản biện và tự sửa chữa Writer–Verifier an toàn: 1. Writer tạo bản nháp ban đầu (draft) (o2) -&gt; 2. Verifier đối chiếu bản nháp với các tiêu chí/hợp đồng và trả về các vi phạm cụ thể (o4) -&gt; 3. Ghi nhận số lần thử (attempt) và phản hồi vào nhật ký trace (o5) -&gt; 4. Nếu chưa đạt và còn ngân sách thử lại, writer sửa theo feedback có tính hành động rồi gửi lại verifier (o1) -&gt; 5. Nếu đạt thì xuất bản, nếu hết ngân sách thì dừng lại và leo thang từ chối (o3).</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Thiết kế như khi gọi một danh tính ngoài tổ chức.</t>
+          <t>Khi tích hợp và gọi một agent đối tác nằm ngoài miền tin cậy (external trust boundary), bên gọi bắt buộc phải: (a) Xác thực danh tính agent/endpoint; (b) Phân quyền chặt chẽ các năng lực và dữ liệu được gửi đi; (c) Thu gọn ngữ cảnh tối thiểu (context minimization / least privilege); (d) Kiểm tra tính toàn vẹn và nguồn gốc của các artifact nhận về. Không được tin tưởng mù quáng chỉ vì agent có tên trong danh mục.</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mỗi kết quả theo contract phải có kiểm tra riêng.</t>
+          <t>Bộ kiểm thử hợp đồng độc lập (contract test suite) cho RetrievalWorker bắt buộc phải bao quát: (a) Truy vấn hợp lệ trả về kết quả đúng schema; (b) Khi không có kết quả phù hợp phải trả về tập rỗng mà không được bịa đặt; (c) Đầu vào không hợp lệ (sai schema) phải bị từ chối rõ ràng; (d) Khi các dịch vụ phụ thuộc (vector DB, embedder) gặp sự cố phải chuyển hóa thành mã lỗi có cấu trúc theo contract. Không thể chỉ chạy một test end-to-end đơn lẻ.</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Định danh phải tồn tại trước snapshot và được dùng lại khi tiếp tục.</t>
+          <t>Quy trình tạm dừng, kiểm tra và tiếp tục (pause, inspect, resume) an toàn trong đồ thị tác nhân: 1. Khởi tạo bộ lưu trữ trạng thái (checkpointer) (o2) -&gt; 2. Thực thi đồ thị với thread ID duy nhất và ổn định (o3) -&gt; 3. Đồ thị dừng lại tại cổng kiểm tra (review gate / interrupt) và lưu snapshot trạng thái (o4) -&gt; 4. Tiếp tục thực thi với cùng thread/run ID từ checkpoint đã duyệt (o1) -&gt; 5. Thực hiện tác vụ có hậu quả ra bên ngoài với chốt chặn idempotent (o5).</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_09_Full_107_Cau/Day_09_Ngan_Hang_Phan_04_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_09_Full_107_Cau/Day_09_Ngan_Hang_Phan_04_21_Cau.xlsx
@@ -673,10 +673,25 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một payload kết quả chưa đủ nếu vòng đời task chưa ở trạng thái kết thúc.
-Phân tích theo nguyên lý thiết kế: Một payload kết quả chưa đủ nếu vòng đời task chưa ở trạng thái kết thúc.</t>
+- [Mô hình hóa vòng đời 5 trạng thái] (1.5 điểm): Vẽ đúng máy trạng thái: SUBMITTED -&gt; IN_PROGRESS -&gt; WAITING_FOR_INPUT -&gt; COMPLETED / FAILED.
+- [Chỉ rõ 2 mâu thuẫn không nhất quán] (1.5 điểm): Vạch trần lỗi mâu thuẫn: artifact đã có file nhưng status vẫn in_progress, và trạng thái chờ dữ liệu không đồng bộ.
+- [Quy tắc nguyên tử khi bàn giao Artifact] (1.0 điểm): Thiết lập bất biến: bàn giao artifact bắt buộc phải đi kèm chuyển trạng thái sang COMPLETED.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Mô hình hóa Vòng đời Tác vụ A2A Chuẩn mực (A2A Task Lifecycle State Machine):
+Vòng đời của một tác vụ A2A bất đồng bộ trải qua 5 trạng thái hữu hạn:
+`SUBMITTED (202 Accepted)` -&gt; `IN_PROGRESS (Đang chạy)` -&gt; `WAITING_FOR_INPUT (Chờ dữ liệu bổ sung)` -&gt; `COMPLETED (Thành công)` HOẶC `FAILED (Thất bại)`.
+2. Chỉ ra các Điểm Không Nhất quán Nghiêm trọng trong Bối cảnh (State Inconsistencies):
+- **Không nhất quán 1: Trạng thái trung gian mập mờ**: Sau khi client gửi task và nhận 202, có một message báo 'đang chờ dữ liệu' nhưng task không được chuyển sang trạng thái chính thức `WAITING_FOR_INPUT`, khiến client không biết có cần gửi thêm thông tin gì không.
+- **Không nhất quán 2: Mâu thuẫn giữa Artifact và Trạng thái kết thúc (Premature Artifact vs Incomplete Status)**:
+  Cuối cùng, artifact đã trả về tệp dữ liệu kết quả hoàn chỉnh, nhưng trạng thái của task vẫn bị kẹt ở `in_progress`. Đây là vi phạm nghiêm trọng Hợp đồng Vòng đời: Client không thể biết tác vụ đã kết thúc hay chưa để đóng tiến trình và giải phóng tài nguyên.
+3. Cách xử lý chuẩn hóa (Standardized State Resolution Protocol):
+- **Quy tắc Bất biến Bàn giao Artifact (Artifact Delivery Invariant)**:
+  Việc bàn giao Artifact kết quả cuối cùng BẮT BUỘC phải đi kèm với việc chuyển trạng thái nguyên tử sang `status = 'COMPLETED'`.
+- Bổ sung bước chuyển tiếp tường minh: Khi cần thêm dữ liệu, phát sự kiện `AWAITING_INPUT` kèm danh sách trường cần bổ sung; khi nhận đủ, chuyển `IN_PROGRESS`; khi tạo xong file artifact, chuyển ngay sang `COMPLETED`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một artifact kết quả không bao giờ có thể coi là hợp lệ nếu trạng thái vòng đời của tác vụ chưa chuyển sang trạng thái kết thúc (Terminal State: COMPLETED). Sự bất nhất quán giữa trạng thái và dữ liệu trả về sẽ dẫn đến việc hệ thống treo vô tận (Zombie Task) hoặc xử lý dữ liệu dở dang.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+REST Asynchronous Task Execution Guidelines &amp; Temporal / Camunda Workflow State Machine Standards</t>
         </is>
       </c>
     </row>
@@ -758,10 +773,43 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Agent từ xa không buộc phải chạy thành công như một lời gọi hàm.
-Phân tích theo nguyên lý thiết kế: Agent từ xa không buộc phải chạy thành công như một lời gọi hàm.</t>
+- [Phê phán lỗi ủy thác hiện tại] (1.0 điểm): Nhận diện lỗi lộ state nội bộ, thiếu deadline dẫn đến chờ 40 phút, và trả văn xuôi không có task ID.
+- [Soạn thảo Delegation Contract chuẩn hóa] (1.5 điểm): Thiết kế schema ủy thác có task_id, deadline_utc, input payload sạch và schema đầu ra có cấu trúc.
+- [Đặc tả các trạng thái phản hồi] (1.5 điểm): Liệt kê đủ các trạng thái phản hồi: Acknowledged, In_Progress (heartbeat), Success, Failed, Timeout.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tích các sai lầm trong ủy thác hiện tại (Flaws in Current Delegation):
+- Truyền toàn bộ state nội bộ vi phạm ranh giới đóng gói dữ liệu và làm lộ bí mật thông tin.
+- Thiếu hạn chót (Deadline/Timeout) khiến client bị treo 40 phút.
+- Thiếu schema đầu ra và thiếu task ID khiến client nhận lại đoạn văn xuôi không biết của task nào và không thể bóc tách tự động bằng code.
+2. Viết lại Hợp đồng Ủy thác Chuẩn mực (Rewritten Delegation Contract):
+```json
+{
+  "task_id": "LEGAL-REV-2026-0082",
+  "task_type": "CONTRACT_REVIEW",
+  "deadline_utc": "2026-10-23T15:15:00Z",
+  "timeout_seconds": 600,
+  "input_payload": {
+    "contract_text": "...nội dung hợp đồng được trích xuất sạch...",
+    "focus_areas": ["liability", "termination_clause"]
+  },
+  "response_schema_required": {
+    "task_id": "string",
+    "status": "APPROVED | REJECTED | REQUIRES_AMENDMENT",
+    "risk_score": "number (0.0 to 1.0)",
+    "flagged_clauses": [{"clause_id": "string", "issue": "string", "recommendation": "string"}]
+  }
+}
+```
+3. Các trạng thái phản hồi của Agent từ xa (Remote Agent Response States):
+- `ACKNOWLEDGED / ACCEPTED`: Xác nhận đã nhận task hợp lệ và bắt đầu xử lý.
+- `IN_PROGRESS`: Báo cáo nhịp tim định kỳ (Heartbeat) kèm tiến độ ước tính.
+- `SUCCESS`: Trả về kết quả đúng schema yêu cầu kèm `task_id` trùng khớp.
+- `FAILED`: Báo cáo lỗi cụ thể kèm mã lỗi nghiệp vụ khi không thể hoàn thành.
+- `TIMEOUT / CANCELLED`: Hủy bỏ tác vụ khi vượt quá 10 phút.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Ủy thác tác tử từ xa (A2A Remote Delegation) không thể hoạt động như một lời gọi hàm cục bộ. Nó đòi hỏi một hợp đồng bất đồng bộ chặt chẽ với hạn chót (Timeout), định dạng kết quả cấu trúc có kiểm soát, và mã tương quan (Task ID) để đối soát dòng chảy phân tán.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic A2A Delegation Protocols &amp; Enterprise Integration Patterns: 'Request-Reply and Asynchronous Messaging'</t>
         </is>
       </c>
     </row>
@@ -886,10 +934,26 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách giai đoạn thu thập bằng chứng khỏi giai đoạn dung hòa/công bố.
-Phân tích theo nguyên lý thiết kế: Tách giai đoạn thu thập bằng chứng khỏi giai đoạn dung hòa/công bố.</t>
+- [Chọn đúng mô hình Parallel Gathering + Consensus] (1.5 điểm): Thiết kế 2 giai đoạn: 3 agent vùng thu thập song song và Arbitrator dung hòa phán quyết.
+- [Phân định quyền sở hữu &amp; Cấm tự công bố] (1.5 điểm): Khẳng định quyền công bố thuộc độc quyền của Arbitrator, cấm 3 agent vùng tự phát ngôn.
+- [Thiết lập điều kiện dừng hữu hạn] (1.0 điểm): Định nghĩa điều kiện hoàn tất khi đủ 3 báo cáo và điều kiện timeout 60s xử lý bất đồng/thiếu hụt.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn và Kết hợp Chế độ Cộng tác (Collaboration Pattern Combination):
+Áp dụng mô hình kết hợp: **Parallel Federated Gathering (Thu thập Liên bang Song song) kết hợp Consensus Arbitrator (Hội đồng Dung hòa Thẩm phán)**.
+- **Giai đoạn 1: Thu thập Độc lập Song song (Parallel Fan-out Evidence Gathering)**:
+  Ba Agent đại diện cho ba khu vực pháp lý (`Agent_US`, `Agent_EU`, `Agent_APAC`) chạy hoàn toàn song song và độc lập. Mỗi agent chỉ thẩm định trên nguồn dữ liệu và luật lệ thuộc khu vực của mình, xuất ra bản thẩm định có chữ ký: `Assessment_Artifact`.
+- **Giai đoạn 2: Dung hòa và Ra quyết định Chung (Consensus Synthesis Gate)**:
+  Một `ArbitratorAgent` (hoặc `GlobalComplianceSupervisor`) nhận cả 3 bản thẩm định, tổng hợp các điều kiện ràng buộc chéo và đưa ra Phán quyết Chung duy nhất.
+2. Phân định Quyền Sở hữu (Ownership Structure):
+- Quyền sở hữu Thẩm định Vùng: Thuộc riêng về từng agent vùng tương ứng.
+- Quyền sở hữu Quyết định Công bố Toàn cục: **Thuộc ĐỘC QUYỀN về `ArbitratorAgent` (hoặc Cổng Phê duyệt Con người)**. Ba agent khu vực tuyệt đối KHÔNG ĐƯỢC tự ý công bố kết quả ra bên ngoài.
+3. Điều kiện Dừng hữu hạn (Stopping Conditions):
+- Điều kiện hoàn thành: Nhận đủ 3 báo cáo hợp lệ từ 3 vùng VÀ Arbitrator hoàn tất phán quyết không có mâu thuẫn.
+- Điều kiện quá hạn: Sau thời gian chờ `timeout = 60s`, nếu một vùng không phản hồi, Arbitrator dừng luồng và thông báo quyết định một phần kèm cờ cảnh báo thiếu dữ liệu vùng đó.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Thiết kế Hệ thống Thẩm định Đa quyền tài phán: Tách rời tuyệt đối giai đoạn thu thập bằng chứng độc lập khỏi giai đoạn ra quyết định và công bố. Việc cấm các agent thành viên tự công bố ngăn chặn việc phát ngôn mâu thuẫn hoặc rò rỉ dữ liệu chưa được kiểm duyệt.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+CrewAI Hierarchical Processes &amp; AutoGen Multi-Agent Group Consensus Protocols</t>
         </is>
       </c>
     </row>
@@ -969,10 +1033,25 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đừng giải timeout dài bằng cách chỉ tăng số lần thử lại.
-Phân tích theo nguyên lý thiết kế: Đừng giải timeout dài bằng cách chỉ tăng số lần thử lại.</t>
+- [Phê phán lỗi Retry Storm của HTTP Sync] (1.0 điểm): Chỉ ra việc gọi sync timeout 30s trên task 15 phút gây lãng phí tài nguyên và không bao giờ thành công.
+- [Thiết kế mô hình bất đồng bộ với HTTP 202] (1.5 điểm): Áp dụng chuẩn POST trả 202 Accepted kèm task_id và endpoint polling/webhook.
+- [Thiết kế Timeout, Polling/Webhook &amp; Hủy tác vụ] (1.5 điểm): Thiết lập timeout 20 phút, cơ chế theo dõi trạng thái và endpoint DELETE để hủy task khi cần.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phê phán thiết kế hiện tại: Việc gọi một tác vụ phân tích nặng mất 15 phút bằng giao thức HTTP Đồng bộ (Synchronous HTTP) với timeout ngắn 30s và thử lại 5 lần là một thảm họa kỹ thuật (Cascading Retry Storm): Cứ sau 30s client lại ngắt và gửi lại từ đầu, khiến server bị quá tải với 5 tiến trình phân tích trùng lặp chạy ngầm và client không bao giờ nhận được kết quả!
+2. Thiết kế lại theo Mô hình Bất đồng bộ Chuẩn mực (Asynchronous Request-Reply Pattern):
+- **Bước 1: Khởi tạo Tác vụ Bất đồng bộ (Task Submission)**:
+  Client gửi `POST /api/v1/analyses` kèm payload -&gt; Server lập tức trả về `HTTP 202 Accepted` trong vòng 100 ms với header `Location: /api/v1/analyses/{task_id}` và payload: `{"task_id": "AN-991", "status": "SUBMITTED", "estimated_duration": 900}`.
+- **Bước 2: Quản lý Timeout và Theo dõi Trạng thái (Polling or Webhook Lifecycle)**:
+  + **Phương án 1 (Webhook Callback - Khuyến nghị)**: Client cung cấp `callback_url`. Khi server phân tích xong sau 15 phút, server chủ động gọi webhook gửi kết quả cho client.
+  + **Phương án 2 (Polling with Backoff)**: Client kiểm tra trạng thái định kỳ `GET /api/v1/analyses/AN-991` với khoảng cách tăng dần (sau 1m, 3m, 5m, 10m). Server trả về `{status: 'PROCESSING', progress_percentage: 45%}`.
+  + **Timeout tổng thể**: Thiết lập timeout tác vụ thực tế là `1.200 giây (20 phút)` (thay vì 30s).
+- **Bước 3: Hủy tác vụ (Task Cancellation)**:
+  Nếu client không còn nhu cầu, gửi lệnh `DELETE /api/v1/analyses/{task_id}` -&gt; Server gửi tín hiệu ngắt (SIGTERM/AbortSignal) để giải phóng tiến trình phân tích.
+- **Bước 4: Lấy Kết quả Cuối cùng**: Khi `status == 'SUCCESS'`, client nhận URL tải kết quả hoặc payload hoàn chỉnh.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Kiến trúc: Các tác vụ dài hơn 5-10 giây bắt buộc phải chuyển dịch từ HTTP Đồng bộ (Sync) sang Mô hình Bất đồng bộ (Asynchronous Job Pattern). Sử dụng HTTP 202 Accepted, Webhook callback và cơ chế Cancellation giúp loại bỏ hoàn toàn các cơn bão retry làm sập máy chủ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+RFC 7231 (HTTP/1.1 Semantics: 202 Accepted) &amp; Enterprise Integration Patterns: 'Asynchronous Request-Reply'</t>
         </is>
       </c>
     </row>
@@ -1052,10 +1131,33 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một vòng lặp phải chứng minh được tiến bộ hoặc dừng lại.
-Phân tích theo nguyên lý thiết kế: Một vòng lặp phải chứng minh được tiến bộ hoặc dừng lại.</t>
+- [Phê phán phản hồi 'not good' và lặp vô tận] (1.0 điểm): Chỉ ra phản hồi thiếu ngữ cảnh khiến writer mò mẫm và gây tốn token/treo hệ thống.
+- [Thiết kế Feedback Contract có cấu trúc] (1.5 điểm): Định nghĩa schema phản hồi chi tiết: error_type, specific_defects, actionable_instruction.
+- [Số vòng tối đa &amp; Cơ chế dừng kết thúc an toàn] (1.5 điểm): Thiết lập giới hạn tối đa 2 vòng và cơ chế dừng chuyển cấp con người khi hết số lượt.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tích nguyên nhân vòng lặp vô tận (Infinite Loop Flaw):
+Hiện tượng: Verifier chỉ trả phản hồi rỗng cụt lủn `not good`, và Writer gọi lại cùng một prompt vô hạn lần. Writer không nhận được bất kỳ thông tin nào về việc 'sai ở đâu và cần sửa gì', dẫn đến việc mò mẫm ngẫu nhiên hoặc lặp lại cùng một câu trả lời. Hệ thống không chứng minh được sự tiến bộ và không có điều kiện dừng.
+2. Thiết kế Hợp đồng Phản hồi Có cấu trúc (Structured Feedback Contract):
+Verifier bắt buộc phải trả về phản hồi theo Schema hướng dẫn hành động (Actionable Feedback Schema), cấm trả text chung chung:
+```json
+{
+  "is_acceptable": false,
+  "error_type": "FACTUAL_ERROR | MISSING_CITATION | OFF_TOPIC",
+  "specific_defects": [
+    {"clause": "Thời hạn 15 ngày", "issue": "Chính sách ghi rõ 30 ngày, sai con số", "expected_correction": "Sửa thành 30 ngày"}
+  ],
+  "actionable_instruction": "Sửa con số thời hạn thành 30 ngày và bổ sung trích dẫn [Doc 2]."
+}
+```
+3. Điều kiện được Thử lại, Số vòng tối đa và Cách kết thúc (Bounded Self-Correction Rules):
+- **Điều kiện được thử lại (Progress Assertion)**: Writer chỉ được chạy lại khi Verifier chỉ ra được lỗi cụ thể có thể sửa được. Prompt gửi lại cho Writer phải được tiêm kèm phản hồi sửa lỗi ở trên.
+- **Số vòng lặp tối đa (Strict Loop Bound)**: Giới hạn tối đa **2 vòng lặp (Max Loops = 2)**.
+- **Cách kết thúc an toàn (Graceful Termination Fallback)**:
+  Nếu sau 2 vòng mà Verifier vẫn đánh giá chưa đạt, hệ thống **DỪNG LẠI NGAY LẬP TỨC**: Chuyển trạng thái sang `FAILED_NEEDS_HUMAN_REVIEW` kèm lịch sử 2 lần sửa để con người can thiệp, hoặc trả về câu trả lời an toàn mặc định.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Tự sửa lỗi có giới hạn (Bounded Self-Correction) là điều kiện sống còn để chống vòng lặp tác tử vô hạn. Một vòng lặp phản hồi chỉ có giá trị khi Verifier cung cấp thông tin sửa lỗi có thể hành động được (Actionable Feedback) và hệ thống có giới hạn cứng về số vòng lặp tối đa.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Madaan et al. (2023): 'Self-Refine: Iterative Refinement with Self-Feedback' &amp; LangGraph Cyclic Execution Bounds</t>
         </is>
       </c>
     </row>
@@ -1179,10 +1281,26 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nếu không có quy tắc khép mâu thuẫn, ai có thẩm quyền bổ sung quy tắc?
-Phân tích theo nguyên lý thiết kế: Nếu không có quy tắc khép mâu thuẫn, ai có thẩm quyền bổ sung quy tắc?</t>
+- [Nhận diện bế tắc thẩm quyền ngang hàng] (1.0 điểm): Nhận định rõ 2 agent không có quyền tự quyết định khi thiếu policy ưu tiên.
+- [Thiết kế quy trình chuyển cấp lên con người] (1.5 điểm): Thiết lập luồng đóng gói hồ sơ xung đột và gửi lên Hội đồng Chính sách/CCO phê duyệt.
+- [Soạn thảo đầu ra an toàn trong lúc chờ] (1.5 điểm): Thiết kế câu trả lời minh bạch cho người dùng: nêu rõ mâu thuẫn giữa 2 nguồn và cấp mã tra cứu theo dõi.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tích bế tắc xung đột thẩm quyền ngang hàng (Peer Conflict Deadlock):
+LegalAgent và RiskAgent viện dẫn hai quy định có cùng ngày hiệu lực, thẩm quyền ngang hàng nhưng yêu cầu hoàn toàn trái ngược nhau. Do hệ thống chưa có chính sách phân xử ưu tiên (No Precedence Policy), không một tác tử nào có thẩm quyền pháp lý để tự ý tuyên bố mình đúng hơn bên kia.
+2. Thiết kế Cơ chế Chuyển cấp (Escalation Architecture):
+- **Bước 1 (Đóng băng và Tạo Phiếu xung đột - Conflict Case Generation)**:
+  Hệ thống phát hiện mâu thuẫn không thể hòa giải -&gt; Lập tức đóng gói hồ sơ xung đột (Conflict Docket) gồm:
+  `{conflict_id, agent_A_claim, agent_A_source, agent_B_claim, agent_B_source, query_context}`.
+- **Bước 2 (Chuyển cấp lên Hội đồng Pháp chế Con người - Human Escalation Route)**:
+  Định tuyến hồ sơ sang Cổng phê duyệt của Trưởng ban Pháp chế &amp; Tuân thủ (Chief Compliance Officer / Policy Committee Dashboard) - Chủ thể duy nhất có thẩm quyền ban hành hoặc giải thích quy tắc ưu tiên chính thức.
+3. Thiết kế Đầu ra An toàn cho Người dùng trong Lúc chờ (Interim Safe Output):
+- **Nguyên tắc**: Tuyệt đối không đưa ra kết luận khẳng định thiên vị một bên nào.
+- **Nội dung thông báo minh bạch cho người dùng**:
+  'Yêu cầu của bạn liên quan đến một quy định đang có sự không đồng nhất giữa Quy chế Pháp chế [Nguồn A] và Hướng dẫn Quản trị Rủi ro [Nguồn B] có cùng ngày hiệu lực. Hệ thống đã tự động chuyển tiếp hồ sơ này (Mã tra cứu: #CONF-2026) đến Hội đồng Chính sách để phê duyệt quyết định cuối cùng. Chúng tôi sẽ phản hồi lại bạn ngay khi có thông báo chính thức.'
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Khi hai tác tử thẩm quyền ngang hàng mâu thuẫn và thiếu quy tắc phân xử nội bộ, việc tự ý quyết định là hành vi vi phạm an toàn pháp lý. Cơ chế Chuyển cấp (Escalation) bảo đảm hệ thống biết dừng đúng lúc, bàn giao quyền quyết định cho con người và cung cấp phản hồi tạm thời minh bạch.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Incident Escalation Patterns &amp; Enterprise Risk Management Framework (COSO)</t>
         </is>
       </c>
     </row>
@@ -1264,10 +1382,24 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Registry trả lời 'có agent nào', không trả lời 'có được gửi dữ liệu này không'.
-Phân tích theo nguyên lý thiết kế: Registry trả lời 'có agent nào', không trả lời 'có được gửi dữ liệu này không'.</t>
+- [Quyết định từ chối ủy thác nguyên bản] (1.0 điểm): Nhận định registry không đồng nghĩa với quyền truy cập dữ liệu; từ chối cấp toàn bộ DB khách hàng.
+- [Thiết kế ngữ cảnh gửi đi tối thiểu hóa PII] (1.5 điểm): Chỉ gửi dữ liệu của duy nhất order cần phân tích, che/băm thông tin định danh cá nhân.
+- [Xử lý Artifact không chữ ký bằng Zero-Trust] (1.5 điểm): Coi artifact là unverified, quét sandbox chống injection và cấm tự động kích hoạt hành động.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Quyết định về việc Ủy thác (Delegation Decision):
+- Quyết định: **TỪ CHỐI ỦY THÁC NGUYÊN BẢN (REJECT BLIND DELEGATION)**.
+- Căn cứ: Yêu cầu 'cung cấp toàn bộ cơ sở dữ liệu khách hàng chỉ để phân tích một order đơn lẻ' là biểu hiện nghiêm trọng của việc vi phạm Ranh giới Tin cậy (Trust Boundary Violation) và vi phạm pháp luật bảo vệ dữ liệu (GDPR/Data Minimization). Sự hiện diện trong Registry chỉ chứng minh agent đó 'tồn tại', hoàn toàn KHÔNG CHỨNG MINH agent đó được phép truy cập dữ liệu nhạy cảm của toàn bộ công ty.
+2. Thiết kế Ngữ cảnh Gửi đi được Kiểm soát (Sanitized Outbound Context):
+- Tuyệt đối cấm gửi toàn bộ cơ sở dữ liệu khách hàng!
+- Áp dụng **Bộ lọc Tối thiểu hóa Dữ liệu (Context Sanitization &amp; Scoping)**: Chỉ đóng gói chính xác các trường dữ liệu phi định danh của duy nhất đơn hàng cần phân tích: `order_items`, `order_amount`, `masked_customer_id` (đã băm SHA-256), và `order_timestamp`. Toàn bộ tên, số điện thoại, địa chỉ và lịch sử các đơn hàng khác đều bị loại bỏ.
+3. Cách Xử lý Artifact trả về không có chữ ký/source (Untrusted Inbound Artifact Handling):
+- **Đánh dấu là Dữ liệu Chưa được Kiểm chứng (Unverified Artifact)**: Vì artifact trả về không có chữ ký số (Digital Signature) và không có nguồn trích dẫn, hệ thống coi đây là dữ liệu có độ tin cậy bằng không.
+- **Bộ lọc Hậu kiểm (Post-processing Verification)**: Đưa artifact qua bộ quét bảo mật (Security Sandbox Scan) để kiểm tra mã độc hoặc prompt injection ẩn.
+- **Chỉ coi là Gợi ý Tham khảo**: Tuyệt đối không cho phép artifact này tự động kích hoạt các hành động giao dịch tài chính nếu không có sự phê duyệt của con người.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Ranh giới tin cậy liên tác tử (Cross-Agent Trust Boundary) tuân thủ nguyên tắc Zero Trust: 'Không tin tưởng bất kỳ tác tử bên ngoài nào'. Dữ liệu gửi đi phải được tối thiểu hóa và làm sạch (Sanitization); dữ liệu nhận về không có chữ ký xác thực phải được đối xử như dữ liệu thô không an toàn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NIST Zero Trust Architecture (SP 800-207) &amp; OWASP Top 10 for LLM: LLM06 &amp; LLM08</t>
         </is>
       </c>
     </row>
@@ -1394,10 +1526,29 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra các bất biến quan sát được, không kiểm tra câu chữ tùy ý.
-Phân tích theo nguyên lý thiết kế: Kiểm tra các bất biến quan sát được, không kiểm tra câu chữ tùy ý.</t>
+- [Phê phán kiểm thử khớp câu chữ mong manh] (1.0 điểm): Nhận diện lỗi brittle test khi so khớp chuỗi trên mô hình sinh ngôn ngữ tự nhiên.
+- [Thiết kế Test Dataset Matrix đa kịch bản] (1.5 điểm): Thiết kế 4 test cases: có chunk, chunk rỗng, mâu thuẫn và nhiễu.
+- [Đặc tả 4 Invariant Assertions bền vững] (1.5 điểm): Định nghĩa các assertion toán học/logic: citation hợp lệ, abstention khi rỗng, confidence thuộc [0, 1] và NLI entailment.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phê phán kiểm thử khớp câu chữ hiện tại (Brittle Exact-String Match Flaw):
+Kiểm thử khớp câu chữ (Exact-match assertion) trên mô hình ngôn ngữ là cực kỳ mong manh và dễ gãy (Brittle Test Defect): LLM có thể thay đổi vài từ đồng nghĩa hoặc đảo cấu trúc câu mà vẫn đúng nghiệp vụ 100%, nhưng test vẫn báo lỗi đỏ; ngược lại, test chỉ kiểm tra 1 câu đơn lẻ sẽ bỏ lọt toàn bộ các vi phạm hợp đồng về citation, độ tin cậy và trường hợp rỗng.
+2. Thiết kế Bộ Dữ liệu Kiểm thử Đa dạng (Test Dataset Matrix):
+- **Case 1 (Có đoạn trích hợp lệ)**: Cung cấp 2 đoạn trích `[Chunk_A, Chunk_B]`. Yêu cầu câu trả lời phải chứa trích dẫn.
+- **Case 2 (Tập đoạn trích rỗng - Zero Context)**: Cung cấp `chunks = []`. Yêu cầu worker phải từ chối trả lời.
+- **Case 3 (Đoạn trích mâu thuẫn)**: Cung cấp 2 đoạn trích trái ngược thông tin để kiểm tra xử lý mâu thuẫn.
+- **Case 4 (Nhiều đoạn trích kèm nhiễu)**: Cung cấp 5 đoạn trích trong đó có 3 đoạn trích rác.
+3. Thiết kế các Kiểm tra Bất biến Bền vững (Robust Property-Based Invariant Assertions):
+- **Invariant 1: Quy tắc Trích dẫn khi có dữ liệu (Citation Invariant)**:
+  `if len(context_chunks) &gt; 0: assert len(response.citations) &gt; 0 and all(c in [chunk.id for chunk in context_chunks] for c in response.citations)`.
+- **Invariant 2: Quy tắc Từ chối khi thiếu dữ liệu (Abstention Invariant)**:
+  `if len(context_chunks) == 0: assert response.is_abstained == True and len(response.citations) == 0`.
+- **Invariant 3: Miền Giá trị Độ tin cậy (Confidence Range Invariant)**:
+  `assert isinstance(response.confidence, float) and 0.0 &lt;= response.confidence &lt;= 1.0`.
+- **Invariant 4: Kiểm tra bám bằng chứng bằng NLI (Entailment Check)**: Dùng mô hình NLI nhỏ (như DeBERTa) kiểm tra `NLI_Entails(context, response.text) == True` thay vì so khớp câu chữ.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Kiểm thử hợp đồng tác tử (Worker Contract Test Harness) đòi hỏi chuyển dịch từ Kiểm thử Chuỗi Tĩnh (Static String Testing) sang Kiểm thử Dựa trên Thuộc tính và Bất biến Quan sát được (Property-Based &amp; Invariant Testing). Điều này giúp bài test bền vững trước các thay đổi về văn phong của mô hình ngôn ngữ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Hypothesis Property-Based Testing Guidelines &amp; LangSmith / TruLens Evaluation Harness Architecture</t>
         </is>
       </c>
     </row>
@@ -1477,10 +1628,25 @@
       <c r="K23" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hỏi snapshot nào được nạp và hành động nào đã/chưa được cam kết thực hiện.
-Phân tích theo nguyên lý thiết kế: Hỏi snapshot nào được nạp và hành động nào đã/chưa được cam kết thực hiện.</t>
+- [Chẩn đoán đúng nguyên nhân double refund] (1.5 điểm): Chỉ ra việc fork thread ID mới và resume song song checkpoint cũ cùng phát sinh 2 lệnh hoàn tiền.
+- [Khóa Thread ID &amp; Chuyển trạng thái nguyên tử] (1.0 điểm): Ràng buộc resume trên đúng thread gốc và atomic state transition 'refunding_in_progress'.
+- [Giải pháp Idempotency Key tầng Payment] (1.5 điểm): Thiết lập mã Idempotency Key duy nhất theo case_id gửi sang cổng thanh toán chống lặp giao dịch.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chẩn đoán nguyên nhân sự cố hoàn tiền hai lần (Double Refund Root Cause Diagnosis):
+- Sự cố phát sinh từ việc phá vỡ tính liên kết luồng và thiếu cơ chế khóa lũy thừa (Thread Decoupling &amp; Missing Idempotency Defect):
+  + Lần chạy A lưu checkpoint ở trạng thái `approved_pending_refund` (đã duyệt nhưng chưa chuyển tiền).
+  + Người vận hành tạo `thread_id` MỚI để tiếp tục, tách rời luồng này khỏi checkpoint cũ; sau đó checkpoint gốc lại được resume tiếp. Kết quả là có hai tiến trình độc lập cùng nạp trạng thái 'chưa hoàn tiền' và cùng phát lệnh hoàn tiền sang cổng thanh toán.
+2. Sửa đổi Contract Lưu và Tiếp tục Trạng thái (Persistence &amp; Resume Contract Repair):
+- **Quy tắc 1: Khóa Luồng Thực thi Đơn nhất (Thread Locking Invariant)**:
+  Một checkpoint chỉ được phép tiếp tục (resume) trên CHÍNH `thread_id` gốc của nó. Hệ thống cấm việc tạo thread ID mới từ một checkpoint đang chờ xử lý mà không có lệnh hủy (Abort/Fork) thread cũ.
+- **Quy tắc 2: Khóa Trạng thái Chuyển tiếp Nguyên tử (Atomic State Lock)**:
+  Trước khi phát lệnh hoàn tiền, node phải thực hiện một chuyển trạng thái nguyên tử (Atomic CAS - Compare-And-Swap): `status: 'approved_pending_refund' -&gt; 'refunding_in_progress'`. Nếu một tiến trình khác đã đổi trạng thái, lệnh thứ hai lập tức bị từ chối.
+- **Quy tắc 3: Mã Khóa Giao dịch Lũy thừa (Payment Idempotency Key - Rào chắn Tối thượng)**:
+  Mọi lệnh gọi API sang Payment Gateway bắt buộc phải đính kèm `Idempotency-Key = hash(case_id)`. Khi cổng thanh toán nhận lệnh thứ hai có cùng key, nó lập tức từ chối giao dịch mới và trả về biên lai của giao dịch đầu tiên, triệt tiêu 100% nguy cơ hoàn tiền hai lần.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong các hệ thống điều phối tác tử có hỗ trợ lưu trữ trạng thái (Persistence &amp; Time-Travel Debugging như LangGraph Checkpointers), việc tiếp tục một checkpoint (Resume) mang tính tác dụng phụ tài chính bắt buộc phải đi kèm với Idempotency Key ở tầng hạ tầng. Snapshot chỉ lưu dữ liệu; chỉ có Idempotency Key mới bảo vệ được giao dịch thực tế.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangGraph Persistence &amp; Checkpointer Documentation &amp; Stripe API Documentation: 'Idempotent Requests'</t>
         </is>
       </c>
     </row>
